--- a/BIOL90042_Group_Project/result/rna_Q2_gene_ontology.xlsx
+++ b/BIOL90042_Group_Project/result/rna_Q2_gene_ontology.xlsx
@@ -25,10 +25,10 @@
     <t>de_genes</t>
   </si>
   <si>
-    <t>up_in_pd</t>
-  </si>
-  <si>
-    <t>down_in_pd</t>
+    <t>upregulated_in_pd</t>
+  </si>
+  <si>
+    <t>downregulated_in_pd</t>
   </si>
   <si>
     <t>gene_names</t>
